--- a/data/raw/collected_metadata/metadata_avis.xlsx
+++ b/data/raw/collected_metadata/metadata_avis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://genes-my.sharepoint.com/personal/lmaurice_ensae_fr/Documents/CCNE/Analyse/CCNE/data/raw/collected_metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leopold.maurice\Documents\Projets - Code\CCNE\data\raw\collected_metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1835" documentId="11_AD4D9D64A577C15A4A54185C681B52125BDEDD8A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83D5DE3-1E80-4810-BBC8-9457DB148488}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4EB1F9-3E44-407B-B679-2B4010436CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-67320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="628">
   <si>
     <t>num</t>
   </si>
@@ -1893,6 +1893,36 @@
   </si>
   <si>
     <t>112;116;109;77;127;105;46;124;120;115;122;126;90;113;26;63;87;108;121;128</t>
+  </si>
+  <si>
+    <t>Le cadre de l'évaluation éthique de la recherche clinique</t>
+  </si>
+  <si>
+    <t>évaluation recherche</t>
+  </si>
+  <si>
+    <t>Enjeux éthiques relatifs au don de plasma et aux médicaments dérivés du plasma en période de pénurie</t>
+  </si>
+  <si>
+    <t>plasma</t>
+  </si>
+  <si>
+    <t>Enjeux éthiques relatifs à la crise de la psychiatrie : une alerte du CCNE</t>
+  </si>
+  <si>
+    <t>crise psychiatrie</t>
+  </si>
+  <si>
+    <t>Enjeux éthiques relatifs aux situations de vulnérabilité liées aux avancées médicales et aux limites du système de soins</t>
+  </si>
+  <si>
+    <t>vulnérabilité</t>
+  </si>
+  <si>
+    <t>Baisse de la natalité et de la fertilité : des réponses différentes, des enjeux éthiques partagés</t>
+  </si>
+  <si>
+    <t>natalité</t>
   </si>
 </sst>
 </file>
@@ -1947,10 +1977,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2216,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -2224,13 +2250,14 @@
     <col min="3" max="3" width="9.5703125" customWidth="1"/>
     <col min="4" max="4" width="46.85546875" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="1" customWidth="1"/>
-    <col min="7" max="8" width="0.140625" customWidth="1"/>
-    <col min="9" max="9" width="0.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="69" customWidth="1"/>
     <col min="11" max="11" width="22.85546875" customWidth="1"/>
-    <col min="12" max="12" width="1.140625" customWidth="1"/>
-    <col min="13" max="13" width="1" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" customWidth="1"/>
     <col min="15" max="15" width="10.85546875" customWidth="1"/>
     <col min="16" max="16" width="3.42578125" customWidth="1"/>
@@ -2293,356 +2320,194 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>144</v>
-      </c>
-      <c r="B2" s="1">
-        <v>44886</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>72</v>
+        <v>149</v>
       </c>
       <c r="I2" t="s">
-        <v>3</v>
+        <v>627</v>
       </c>
       <c r="J2" t="s">
-        <v>2</v>
+        <v>626</v>
       </c>
       <c r="K2" s="1">
-        <v>45113</v>
-      </c>
-      <c r="L2" t="b">
-        <f>FALSE</f>
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>256</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>562</v>
+        <v>45715</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>148</v>
+      </c>
+      <c r="I3" t="s">
+        <v>625</v>
+      </c>
+      <c r="J3" t="s">
+        <v>624</v>
+      </c>
+      <c r="K3" s="1">
+        <v>45687</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>147</v>
+      </c>
+      <c r="I4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J4" t="s">
+        <v>622</v>
+      </c>
+      <c r="K4" s="1">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>146</v>
+      </c>
+      <c r="I5" t="s">
+        <v>621</v>
+      </c>
+      <c r="J5" t="s">
+        <v>620</v>
+      </c>
+      <c r="K5" s="1">
+        <v>45645</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>145</v>
+      </c>
+      <c r="I6" t="s">
+        <v>619</v>
+      </c>
+      <c r="J6" t="s">
+        <v>618</v>
+      </c>
+      <c r="K6" s="1">
+        <v>45379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>144</v>
+      </c>
+      <c r="B7" s="1">
+        <v>44886</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" t="s">
+        <v>524</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>45113</v>
+      </c>
+      <c r="L7" t="b">
+        <f>FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>256</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>143</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D8" t="s">
         <v>541</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E8" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F8" t="s">
         <v>542</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" t="s">
         <v>4</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J8" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K8" s="1">
         <v>44973</v>
       </c>
-      <c r="L3" t="b">
+      <c r="L8" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M8" t="s">
         <v>44</v>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3">
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P8" t="s">
         <v>514</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q8" t="s">
         <v>563</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>142</v>
-      </c>
-      <c r="B4" s="1">
-        <v>44743</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>525</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="1">
-        <v>44973</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>141</v>
-      </c>
-      <c r="B5" s="1">
-        <v>43661</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>541</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>543</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="1">
-        <v>45254</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>140</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="1">
-        <v>44854</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>139</v>
-      </c>
-      <c r="B7" s="2">
-        <v>44348</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" t="s">
-        <v>122</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="1">
-        <v>44742</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>138</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>526</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="1">
-        <v>44336</v>
-      </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>137</v>
+        <v>142</v>
+      </c>
+      <c r="B9" s="1">
+        <v>44743</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>525</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2654,19 +2519,19 @@
         <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
-        <v>44336</v>
+        <v>44973</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -2675,21 +2540,27 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>136</v>
+        <v>141</v>
+      </c>
+      <c r="B10" s="1">
+        <v>43661</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>541</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>543</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2698,19 +2569,19 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="K10" s="1">
-        <v>44301</v>
+        <v>45254</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -2719,24 +2590,21 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>135</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>527</v>
-      </c>
-      <c r="F11" t="s">
-        <v>540</v>
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2745,48 +2613,48 @@
         <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="J11" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1">
-        <v>44159</v>
+        <v>44854</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="P11" t="s">
-        <v>528</v>
-      </c>
       <c r="Q11" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>134</v>
+        <v>139</v>
+      </c>
+      <c r="B12" s="2">
+        <v>44348</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>529</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2795,39 +2663,39 @@
         <v>72</v>
       </c>
       <c r="I12" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="J12" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K12" s="1">
-        <v>43853</v>
+        <v>44742</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>520</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2839,19 +2707,19 @@
         <v>72</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="K13" s="1">
-        <v>43727</v>
+        <v>44336</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -2860,21 +2728,18 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>132</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2886,51 +2751,42 @@
         <v>72</v>
       </c>
       <c r="I14" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K14" s="1">
-        <v>43727</v>
+        <v>44336</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q14">
-        <v>129</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131</v>
-      </c>
-      <c r="B15" s="1">
-        <v>42375</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2939,19 +2795,19 @@
         <v>72</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="K15" s="1">
-        <v>43643</v>
+        <v>44301</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -2959,25 +2815,25 @@
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="Q15">
-        <v>129</v>
+      <c r="Q15" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
+        <v>527</v>
+      </c>
+      <c r="F16" t="s">
+        <v>540</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2986,72 +2842,69 @@
         <v>72</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="J16" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="K16" s="1">
-        <v>43645</v>
+        <v>44159</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>213</v>
+        <v>528</v>
       </c>
       <c r="Q16" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>129</v>
-      </c>
-      <c r="B17" s="2">
-        <v>43252</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
+        <v>529</v>
+      </c>
+      <c r="F17" t="s">
+        <v>71</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="s">
         <v>72</v>
       </c>
       <c r="I17" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J17" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="K17" s="1">
-        <v>43361</v>
+        <v>43853</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -3060,21 +2913,18 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>617</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>128</v>
-      </c>
-      <c r="C18" t="s">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>520</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>552</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3086,39 +2936,42 @@
         <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="J18" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="K18" s="1">
-        <v>43146</v>
+        <v>43727</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>127</v>
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>530</v>
+        <v>76</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3130,36 +2983,48 @@
         <v>72</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="K19" s="1">
-        <v>43024</v>
+        <v>43727</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P19" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q19">
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="B20" s="1">
+        <v>42375</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3171,39 +3036,42 @@
         <v>72</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="J20" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="K20" s="1">
-        <v>42901</v>
+        <v>43643</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="N20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="Q20" t="s">
-        <v>576</v>
+      <c r="Q20">
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>125</v>
+        <v>130</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>531</v>
+        <v>85</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -3215,19 +3083,19 @@
         <v>72</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="K21" s="1">
-        <v>42893</v>
+        <v>43645</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -3235,43 +3103,52 @@
       <c r="O21">
         <v>0</v>
       </c>
-      <c r="Q21">
-        <v>92</v>
+      <c r="P21" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>124</v>
+        <v>129</v>
+      </c>
+      <c r="B22" s="2">
+        <v>43252</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>532</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>72</v>
       </c>
       <c r="I22" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="K22" s="1">
-        <v>42542</v>
+        <v>43361</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -3280,21 +3157,21 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>577</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>521</v>
+        <v>97</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -3306,19 +3183,19 @@
         <v>72</v>
       </c>
       <c r="I23" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="J23" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="K23" s="1">
-        <v>42091</v>
+        <v>43146</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -3326,25 +3203,19 @@
       <c r="O23">
         <v>1</v>
       </c>
-      <c r="P23" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q23">
-        <v>120</v>
+      <c r="Q23" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>122</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>530</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -3356,95 +3227,80 @@
         <v>72</v>
       </c>
       <c r="I24" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s">
-        <v>116</v>
-      </c>
-      <c r="K24" s="2">
-        <v>41671</v>
+        <v>99</v>
+      </c>
+      <c r="K24" s="1">
+        <v>43024</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>121</v>
-      </c>
-      <c r="B25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>533</v>
+        <v>106</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" s="1">
+        <v>42901</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="s">
-        <v>72</v>
-      </c>
-      <c r="I25" t="s">
-        <v>121</v>
-      </c>
-      <c r="J25" t="s">
-        <v>120</v>
-      </c>
-      <c r="K25" s="1">
-        <v>41455</v>
-      </c>
-      <c r="L25" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" t="s">
-        <v>46</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
       <c r="O25">
-        <v>1</v>
-      </c>
-      <c r="P25" t="s">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>120</v>
-      </c>
-      <c r="C26" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>531</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -3456,19 +3312,19 @@
         <v>72</v>
       </c>
       <c r="I26" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="J26" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="K26" s="1">
-        <v>41389</v>
+        <v>42893</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -3476,22 +3332,19 @@
       <c r="O26">
         <v>0</v>
       </c>
-      <c r="Q26" t="s">
-        <v>580</v>
+      <c r="Q26">
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>119</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s">
-        <v>133</v>
+        <v>532</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -3503,19 +3356,19 @@
         <v>72</v>
       </c>
       <c r="I27" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="J27" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="K27" s="1">
-        <v>41326</v>
+        <v>42542</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -3523,25 +3376,22 @@
       <c r="O27">
         <v>0</v>
       </c>
-      <c r="P27" t="s">
-        <v>204</v>
-      </c>
       <c r="Q27" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>139</v>
+        <v>521</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -3553,13 +3403,13 @@
         <v>72</v>
       </c>
       <c r="I28" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="J28" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="K28" s="1">
-        <v>41179</v>
+        <v>42091</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -3571,27 +3421,27 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>582</v>
+        <v>207</v>
+      </c>
+      <c r="Q28">
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>534</v>
+        <v>119</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -3603,19 +3453,19 @@
         <v>72</v>
       </c>
       <c r="I29" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="J29" t="s">
-        <v>141</v>
-      </c>
-      <c r="K29" s="1">
-        <v>40962</v>
+        <v>116</v>
+      </c>
+      <c r="K29" s="2">
+        <v>41671</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -3624,62 +3474,74 @@
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>116</v>
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
-        <v>146</v>
+        <v>533</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
         <v>72</v>
       </c>
       <c r="I30" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="J30" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="K30" s="1">
-        <v>40962</v>
+        <v>41455</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>115</v>
+        <v>120</v>
+      </c>
+      <c r="C31" t="s">
+        <v>134</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -3691,39 +3553,42 @@
         <v>72</v>
       </c>
       <c r="I31" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="J31" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="K31" s="1">
-        <v>40640</v>
+        <v>41389</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>473</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
-        <v>535</v>
+        <v>133</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3735,19 +3600,19 @@
         <v>72</v>
       </c>
       <c r="I32" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="J32" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="K32" s="1">
-        <v>40668</v>
+        <v>41326</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -3756,21 +3621,24 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="Q32" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3782,19 +3650,19 @@
         <v>72</v>
       </c>
       <c r="I33" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="J33" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="K33" s="1">
-        <v>40584</v>
+        <v>41179</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -3802,22 +3670,25 @@
       <c r="O33">
         <v>0</v>
       </c>
+      <c r="P33" t="s">
+        <v>137</v>
+      </c>
       <c r="Q33" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
-        <v>162</v>
+        <v>534</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -3829,42 +3700,39 @@
         <v>72</v>
       </c>
       <c r="I34" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J34" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="K34" s="1">
-        <v>40472</v>
+        <v>40962</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="N34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>111</v>
-      </c>
-      <c r="C35" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3876,19 +3744,19 @@
         <v>72</v>
       </c>
       <c r="I35" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="J35" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="K35" s="1">
-        <v>40185</v>
+        <v>40962</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -3896,25 +3764,19 @@
       <c r="O35">
         <v>0</v>
       </c>
-      <c r="P35" t="s">
-        <v>504</v>
-      </c>
       <c r="Q35">
-        <v>89</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>110</v>
-      </c>
-      <c r="C36" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="E36" t="s">
-        <v>536</v>
+        <v>150</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3926,42 +3788,39 @@
         <v>72</v>
       </c>
       <c r="I36" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="J36" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="K36" s="1">
-        <v>40269</v>
+        <v>40640</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="N36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36">
         <v>0</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>473</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3973,19 +3832,19 @@
         <v>72</v>
       </c>
       <c r="I37" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="J37" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="K37" s="1">
-        <v>40213</v>
+        <v>40668</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -3993,22 +3852,22 @@
       <c r="O37">
         <v>0</v>
       </c>
-      <c r="Q37">
-        <v>45</v>
+      <c r="P37" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>108</v>
-      </c>
-      <c r="C38" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -4020,19 +3879,19 @@
         <v>72</v>
       </c>
       <c r="I38" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="J38" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="K38" s="1">
-        <v>40129</v>
+        <v>40584</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -4040,22 +3899,22 @@
       <c r="O38">
         <v>0</v>
       </c>
-      <c r="P38" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q38">
-        <v>101</v>
+      <c r="Q38" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>107</v>
+        <v>112</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="E39" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -4067,42 +3926,42 @@
         <v>72</v>
       </c>
       <c r="I39" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="J39" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="K39" s="1">
-        <v>40101</v>
+        <v>40472</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="N39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>505</v>
+        <v>196</v>
       </c>
       <c r="D40" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E40" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -4114,19 +3973,19 @@
         <v>72</v>
       </c>
       <c r="I40" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="J40" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="K40" s="1">
-        <v>39849</v>
+        <v>40185</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -4135,21 +3994,24 @@
         <v>0</v>
       </c>
       <c r="P40" t="s">
-        <v>210</v>
+        <v>504</v>
+      </c>
+      <c r="Q40">
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>536</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -4161,19 +4023,19 @@
         <v>72</v>
       </c>
       <c r="I41" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="J41" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="K41" s="1">
-        <v>39730</v>
+        <v>40269</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -4182,21 +4044,21 @@
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E42" t="s">
-        <v>192</v>
+        <v>537</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -4208,19 +4070,19 @@
         <v>72</v>
       </c>
       <c r="I42" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="J42" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="K42" s="1">
-        <v>39597</v>
+        <v>40213</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -4228,31 +4090,25 @@
       <c r="O42">
         <v>0</v>
       </c>
-      <c r="P42" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>561</v>
+      <c r="Q42">
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>103</v>
-      </c>
-      <c r="B43" s="1">
-        <v>39127</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="D43" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E43" t="s">
-        <v>538</v>
-      </c>
-      <c r="F43" t="s">
-        <v>539</v>
+        <v>176</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4261,19 +4117,19 @@
         <v>72</v>
       </c>
       <c r="I43" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="J43" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="K43" s="1">
-        <v>39422</v>
+        <v>40129</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -4282,27 +4138,21 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>560</v>
+        <v>221</v>
+      </c>
+      <c r="Q43">
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>102</v>
-      </c>
-      <c r="B44" s="1">
-        <v>38543</v>
-      </c>
-      <c r="C44" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -4314,19 +4164,19 @@
         <v>72</v>
       </c>
       <c r="I44" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="J44" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="K44" s="1">
-        <v>39394</v>
+        <v>40101</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -4334,22 +4184,22 @@
       <c r="O44">
         <v>0</v>
       </c>
-      <c r="P44" t="s">
-        <v>202</v>
-      </c>
       <c r="Q44" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>101</v>
+        <v>106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>505</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -4361,19 +4211,19 @@
         <v>72</v>
       </c>
       <c r="I45" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="J45" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="K45" s="1">
-        <v>39261</v>
+        <v>39849</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -4381,22 +4231,19 @@
       <c r="O45">
         <v>0</v>
       </c>
-      <c r="Q45">
-        <v>57</v>
+      <c r="P45" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>100</v>
-      </c>
-      <c r="B46" s="1">
-        <v>39358</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
@@ -4411,19 +4258,19 @@
         <v>72</v>
       </c>
       <c r="I46" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="J46" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="K46" s="1">
-        <v>39364</v>
+        <v>39730</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -4431,25 +4278,22 @@
       <c r="O46">
         <v>0</v>
       </c>
-      <c r="P46" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q46">
-        <v>90</v>
+      <c r="Q46" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>509</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="E47" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -4461,19 +4305,19 @@
         <v>72</v>
       </c>
       <c r="I47" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="J47" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="K47" s="1">
-        <v>39329</v>
+        <v>39597</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -4482,24 +4326,30 @@
         <v>0</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>204</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="B48" s="1">
+        <v>39127</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="E48" t="s">
-        <v>233</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
+        <v>538</v>
+      </c>
+      <c r="F48" t="s">
+        <v>539</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -4508,19 +4358,19 @@
         <v>72</v>
       </c>
       <c r="I48" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="J48" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="K48" s="1">
-        <v>39253</v>
+        <v>39422</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -4528,25 +4378,28 @@
       <c r="O48">
         <v>0</v>
       </c>
-      <c r="Q48">
-        <v>77</v>
+      <c r="P48" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B49" s="1">
-        <v>38727</v>
+        <v>38543</v>
       </c>
       <c r="C49" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="D49" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="E49" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -4558,19 +4411,19 @@
         <v>72</v>
       </c>
       <c r="I49" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="J49" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="K49" s="1">
-        <v>39212</v>
+        <v>39394</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
       </c>
       <c r="M49" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -4579,24 +4432,21 @@
         <v>0</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q49">
-        <v>83</v>
+        <v>202</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="E50" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -4608,42 +4458,45 @@
         <v>72</v>
       </c>
       <c r="I50" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="J50" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="K50" s="1">
-        <v>39148</v>
+        <v>39261</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B51" s="1">
-        <v>38813</v>
+        <v>39358</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="D51" t="s">
-        <v>523</v>
+        <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -4655,19 +4508,19 @@
         <v>72</v>
       </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="J51" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="K51" s="1">
-        <v>39119</v>
+        <v>39364</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -4676,27 +4529,24 @@
         <v>0</v>
       </c>
       <c r="P51" t="s">
-        <v>306</v>
+        <v>222</v>
       </c>
       <c r="Q51">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>94</v>
-      </c>
-      <c r="B52" s="1">
-        <v>38355</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>196</v>
+        <v>509</v>
       </c>
       <c r="D52" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="E52" t="s">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -4708,19 +4558,19 @@
         <v>72</v>
       </c>
       <c r="I52" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="J52" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="K52" s="1">
-        <v>39016</v>
+        <v>39329</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -4729,21 +4579,21 @@
         <v>0</v>
       </c>
       <c r="P52" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="E53" t="s">
-        <v>544</v>
+        <v>233</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4755,48 +4605,45 @@
         <v>72</v>
       </c>
       <c r="I53" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="J53" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="K53" s="1">
-        <v>38890</v>
+        <v>39253</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="N53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
-      <c r="P53" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>558</v>
+      <c r="Q53">
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B54" s="1">
-        <v>38879</v>
+        <v>38727</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="D54" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -4808,19 +4655,19 @@
         <v>72</v>
       </c>
       <c r="I54" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="J54" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="K54" s="1">
-        <v>38890</v>
+        <v>39212</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -4829,24 +4676,24 @@
         <v>0</v>
       </c>
       <c r="P54" t="s">
-        <v>263</v>
+        <v>239</v>
+      </c>
+      <c r="Q54">
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>91</v>
-      </c>
-      <c r="B55">
-        <v>2004</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -4858,45 +4705,42 @@
         <v>72</v>
       </c>
       <c r="I55" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="J55" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="K55" s="1">
-        <v>38764</v>
+        <v>39148</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
-      </c>
-      <c r="P55" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>90</v>
+        <v>95</v>
+      </c>
+      <c r="B56" s="1">
+        <v>38813</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="D56" t="s">
-        <v>270</v>
+        <v>523</v>
       </c>
       <c r="E56" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4908,48 +4752,48 @@
         <v>72</v>
       </c>
       <c r="I56" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="J56" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="K56" s="1">
-        <v>38680</v>
+        <v>39119</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="N56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56" t="s">
-        <v>556</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>555</v>
+        <v>306</v>
+      </c>
+      <c r="Q56">
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B57" s="1">
-        <v>38566</v>
+        <v>38355</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="E57" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -4961,42 +4805,42 @@
         <v>72</v>
       </c>
       <c r="I57" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="J57" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="K57" s="1">
-        <v>38617</v>
+        <v>39016</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
       </c>
       <c r="O57">
         <v>0</v>
+      </c>
+      <c r="P57" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>88</v>
-      </c>
-      <c r="B58" s="1">
-        <v>38316</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="E58" t="s">
-        <v>277</v>
+        <v>544</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -5008,19 +4852,19 @@
         <v>72</v>
       </c>
       <c r="I58" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="J58" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="K58" s="1">
-        <v>38526</v>
+        <v>38890</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
@@ -5029,18 +4873,27 @@
         <v>0</v>
       </c>
       <c r="P58" t="s">
-        <v>279</v>
+        <v>255</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>87</v>
+        <v>92</v>
+      </c>
+      <c r="B59" s="1">
+        <v>38879</v>
+      </c>
+      <c r="C59" t="s">
+        <v>134</v>
       </c>
       <c r="D59" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E59" t="s">
-        <v>545</v>
+        <v>21</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -5052,19 +4905,19 @@
         <v>72</v>
       </c>
       <c r="I59" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="J59" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K59" s="1">
-        <v>38821</v>
+        <v>38890</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -5072,25 +4925,25 @@
       <c r="O59">
         <v>0</v>
       </c>
-      <c r="Q59" t="s">
-        <v>616</v>
+      <c r="P59" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>86</v>
-      </c>
-      <c r="B60" s="2">
-        <v>37987</v>
+        <v>91</v>
+      </c>
+      <c r="B60">
+        <v>2004</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="D60" t="s">
-        <v>522</v>
+        <v>266</v>
       </c>
       <c r="E60" t="s">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -5102,19 +4955,19 @@
         <v>72</v>
       </c>
       <c r="I60" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="J60" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="K60" s="1">
-        <v>38295</v>
+        <v>38764</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -5122,25 +4975,25 @@
       <c r="O60">
         <v>0</v>
       </c>
-      <c r="Q60">
-        <v>46</v>
+      <c r="P60" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>85</v>
-      </c>
-      <c r="B61" s="1">
-        <v>38265</v>
+        <v>90</v>
       </c>
       <c r="C61" t="s">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="E61" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -5152,45 +5005,48 @@
         <v>72</v>
       </c>
       <c r="I61" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="J61" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="K61" s="1">
-        <v>38295</v>
+        <v>38680</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="N61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
-      <c r="Q61">
-        <v>79</v>
+      <c r="P61" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B62" s="1">
-        <v>37811</v>
+        <v>38566</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="E62" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -5202,51 +5058,45 @@
         <v>72</v>
       </c>
       <c r="I62" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="J62" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="K62" s="1">
-        <v>38086</v>
+        <v>38617</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
-      </c>
-      <c r="P62" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B63" s="1">
-        <v>37609</v>
+        <v>38316</v>
       </c>
       <c r="C63" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="D63" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="E63" t="s">
-        <v>546</v>
-      </c>
-      <c r="F63" t="s">
-        <v>547</v>
+        <v>277</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -5255,48 +5105,39 @@
         <v>72</v>
       </c>
       <c r="I63" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="J63" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="K63" s="1">
-        <v>37973</v>
+        <v>38526</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
       </c>
       <c r="M63" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="N63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>615</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>82</v>
-      </c>
-      <c r="B64" s="1">
-        <v>37306</v>
-      </c>
-      <c r="C64" t="s">
-        <v>238</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="E64" t="s">
-        <v>304</v>
+        <v>545</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -5308,19 +5149,19 @@
         <v>72</v>
       </c>
       <c r="I64" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="J64" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="K64" s="1">
-        <v>38023</v>
+        <v>38821</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
       </c>
       <c r="M64" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -5328,31 +5169,28 @@
       <c r="O64">
         <v>0</v>
       </c>
-      <c r="P64" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q64">
-        <v>45</v>
+      <c r="Q64" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>81</v>
-      </c>
-      <c r="B65" s="1">
-        <v>36280</v>
+        <v>86</v>
+      </c>
+      <c r="B65" s="2">
+        <v>37987</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="D65" t="s">
-        <v>308</v>
+        <v>522</v>
       </c>
       <c r="E65" t="s">
-        <v>548</v>
-      </c>
-      <c r="F65" t="s">
-        <v>309</v>
+        <v>286</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -5361,19 +5199,19 @@
         <v>72</v>
       </c>
       <c r="I65" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="J65" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="K65" s="1">
-        <v>37942</v>
+        <v>38295</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -5381,25 +5219,25 @@
       <c r="O65">
         <v>0</v>
       </c>
-      <c r="Q65" t="s">
-        <v>614</v>
+      <c r="Q65">
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B66" s="1">
-        <v>37558</v>
+        <v>38265</v>
       </c>
       <c r="C66" t="s">
-        <v>238</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -5411,19 +5249,19 @@
         <v>72</v>
       </c>
       <c r="I66" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="J66" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="K66" s="1">
-        <v>37959</v>
+        <v>38295</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -5431,28 +5269,25 @@
       <c r="O66">
         <v>0</v>
       </c>
-      <c r="P66" t="s">
-        <v>313</v>
-      </c>
       <c r="Q66">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B67" s="1">
-        <v>37713</v>
+        <v>37811</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="E67" t="s">
-        <v>549</v>
+        <v>299</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -5464,19 +5299,19 @@
         <v>72</v>
       </c>
       <c r="I67" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="J67" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="K67" s="1">
-        <v>37882</v>
+        <v>38086</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>158</v>
+        <v>215</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -5484,28 +5319,31 @@
       <c r="O67">
         <v>0</v>
       </c>
+      <c r="P67" t="s">
+        <v>293</v>
+      </c>
       <c r="Q67" t="s">
-        <v>613</v>
+        <v>554</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B68" s="1">
-        <v>36287</v>
+        <v>37609</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>238</v>
       </c>
       <c r="D68" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E68" t="s">
-        <v>550</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
+        <v>546</v>
+      </c>
+      <c r="F68" t="s">
+        <v>547</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -5514,19 +5352,19 @@
         <v>72</v>
       </c>
       <c r="I68" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="J68" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="K68" s="1">
-        <v>37882</v>
+        <v>37973</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -5535,21 +5373,27 @@
         <v>0</v>
       </c>
       <c r="P68" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="Q68" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>77</v>
+        <v>82</v>
+      </c>
+      <c r="B69" s="1">
+        <v>37306</v>
+      </c>
+      <c r="C69" t="s">
+        <v>238</v>
       </c>
       <c r="D69" t="s">
-        <v>518</v>
+        <v>303</v>
       </c>
       <c r="E69" t="s">
-        <v>551</v>
+        <v>304</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -5561,48 +5405,51 @@
         <v>72</v>
       </c>
       <c r="I69" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="J69" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="K69" s="1">
-        <v>37700</v>
+        <v>38023</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
       </c>
       <c r="M69" t="s">
-        <v>44</v>
+        <v>256</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
       </c>
       <c r="O69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="s">
-        <v>339</v>
+        <v>305</v>
+      </c>
+      <c r="Q69">
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B70" s="1">
-        <v>37706</v>
+        <v>36280</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="E70" t="s">
-        <v>327</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
+        <v>548</v>
+      </c>
+      <c r="F70" t="s">
+        <v>309</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -5611,19 +5458,19 @@
         <v>72</v>
       </c>
       <c r="I70" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="J70" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="K70" s="1">
-        <v>37735</v>
+        <v>37942</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -5632,21 +5479,24 @@
         <v>0</v>
       </c>
       <c r="Q70" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="B71" s="1">
+        <v>37558</v>
       </c>
       <c r="C71" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="D71" t="s">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -5658,48 +5508,48 @@
         <v>72</v>
       </c>
       <c r="I71" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="J71" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="K71" s="1">
-        <v>37602</v>
+        <v>37959</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>610</v>
+        <v>313</v>
+      </c>
+      <c r="Q71">
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B72" s="1">
-        <v>37368</v>
+        <v>37713</v>
       </c>
       <c r="C72" t="s">
         <v>134</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>549</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -5711,19 +5561,19 @@
         <v>72</v>
       </c>
       <c r="I72" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="J72" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="K72" s="1">
-        <v>37602</v>
+        <v>37882</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
@@ -5731,25 +5581,25 @@
       <c r="O72">
         <v>0</v>
       </c>
-      <c r="P72" t="s">
-        <v>336</v>
+      <c r="Q72" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B73" s="1">
-        <v>37151</v>
+        <v>36287</v>
       </c>
       <c r="C73" t="s">
-        <v>238</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="E73" t="s">
-        <v>338</v>
+        <v>550</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -5761,19 +5611,19 @@
         <v>72</v>
       </c>
       <c r="I73" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="J73" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="K73" s="1">
-        <v>37525</v>
+        <v>37882</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -5782,24 +5632,21 @@
         <v>0</v>
       </c>
       <c r="P73" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q73">
-        <v>2</v>
+        <v>321</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>72</v>
-      </c>
-      <c r="B74">
-        <v>2001</v>
+        <v>77</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>518</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -5811,48 +5658,45 @@
         <v>72</v>
       </c>
       <c r="I74" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="J74" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="K74" s="1">
-        <v>37441</v>
+        <v>37700</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
       </c>
       <c r="M74" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N74" t="b">
         <v>0</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>609</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B75" s="1">
-        <v>37054</v>
+        <v>37706</v>
       </c>
       <c r="C75" t="s">
-        <v>238</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -5864,19 +5708,19 @@
         <v>72</v>
       </c>
       <c r="I75" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="J75" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="K75" s="1">
-        <v>37371</v>
+        <v>37735</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -5884,16 +5728,16 @@
       <c r="O75">
         <v>0</v>
       </c>
-      <c r="P75" t="s">
-        <v>346</v>
-      </c>
       <c r="Q75" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>70</v>
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>278</v>
       </c>
       <c r="D76" t="s">
         <v>21</v>
@@ -5911,33 +5755,42 @@
         <v>72</v>
       </c>
       <c r="I76" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="J76" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="K76" s="1">
-        <v>37238</v>
+        <v>37602</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P76" t="s">
+        <v>330</v>
       </c>
       <c r="Q76" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>69</v>
+        <v>74</v>
+      </c>
+      <c r="B77" s="1">
+        <v>37368</v>
+      </c>
+      <c r="C77" t="s">
+        <v>134</v>
       </c>
       <c r="D77" t="s">
         <v>21</v>
@@ -5955,19 +5808,19 @@
         <v>72</v>
       </c>
       <c r="I77" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="J77" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="K77" s="1">
-        <v>37203</v>
+        <v>37602</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
@@ -5975,25 +5828,25 @@
       <c r="O77">
         <v>0</v>
       </c>
-      <c r="Q77">
-        <v>56</v>
+      <c r="P77" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B78" s="1">
-        <v>36965</v>
+        <v>37151</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>238</v>
       </c>
       <c r="D78" t="s">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -6005,19 +5858,19 @@
         <v>72</v>
       </c>
       <c r="I78" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="J78" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="K78" s="1">
-        <v>37040</v>
+        <v>37525</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -6026,18 +5879,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>606</v>
+        <v>335</v>
+      </c>
+      <c r="Q78">
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>67</v>
-      </c>
-      <c r="C79" t="s">
-        <v>13</v>
+        <v>72</v>
+      </c>
+      <c r="B79">
+        <v>2001</v>
       </c>
       <c r="D79" t="s">
         <v>21</v>
@@ -6055,42 +5908,42 @@
         <v>72</v>
       </c>
       <c r="I79" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="J79" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="K79" s="1">
-        <v>36909</v>
+        <v>37441</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="Q79" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B80" s="1">
-        <v>36803</v>
+        <v>37054</v>
       </c>
       <c r="C80" t="s">
-        <v>510</v>
+        <v>238</v>
       </c>
       <c r="D80" t="s">
         <v>21</v>
@@ -6108,36 +5961,36 @@
         <v>72</v>
       </c>
       <c r="I80" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="J80" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="K80" s="1">
-        <v>36853</v>
+        <v>37371</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
       </c>
       <c r="M80" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80" t="s">
-        <v>358</v>
+        <v>346</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>65</v>
-      </c>
-      <c r="C81" t="s">
-        <v>238</v>
+        <v>70</v>
       </c>
       <c r="D81" t="s">
         <v>21</v>
@@ -6155,42 +6008,33 @@
         <v>72</v>
       </c>
       <c r="I81" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="J81" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="K81" s="1">
-        <v>36783</v>
+        <v>37238</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>1</v>
-      </c>
-      <c r="P81" t="s">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>64</v>
-      </c>
-      <c r="B82" s="1">
-        <v>36567</v>
-      </c>
-      <c r="C82" t="s">
-        <v>511</v>
+        <v>69</v>
       </c>
       <c r="D82" t="s">
         <v>21</v>
@@ -6208,33 +6052,39 @@
         <v>72</v>
       </c>
       <c r="I82" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="J82" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="K82" s="1">
-        <v>36685</v>
+        <v>37203</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>42</v>
+        <v>179</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
-      <c r="P82" t="s">
-        <v>366</v>
+      <c r="Q82">
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>63</v>
+        <v>68</v>
+      </c>
+      <c r="B83" s="1">
+        <v>36965</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
       </c>
       <c r="D83" t="s">
         <v>21</v>
@@ -6252,19 +6102,19 @@
         <v>72</v>
       </c>
       <c r="I83" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="J83" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="K83" s="1">
-        <v>36552</v>
+        <v>37040</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N83" t="b">
         <v>0</v>
@@ -6273,21 +6123,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="Q83" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>62</v>
-      </c>
-      <c r="B84" s="1">
-        <v>35969</v>
+        <v>67</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
@@ -6305,36 +6152,42 @@
         <v>72</v>
       </c>
       <c r="I84" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="J84" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="K84" s="1">
-        <v>36482</v>
+        <v>36909</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84" t="s">
-        <v>372</v>
-      </c>
-      <c r="Q84">
-        <v>57</v>
+        <v>357</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="B85" s="1">
+        <v>36803</v>
+      </c>
+      <c r="C85" t="s">
+        <v>510</v>
       </c>
       <c r="D85" t="s">
         <v>21</v>
@@ -6352,33 +6205,36 @@
         <v>72</v>
       </c>
       <c r="I85" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="J85" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="K85" s="1">
-        <v>36322</v>
+        <v>36853</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85">
         <v>0</v>
+      </c>
+      <c r="P85" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="D86" t="s">
         <v>21</v>
@@ -6396,13 +6252,13 @@
         <v>72</v>
       </c>
       <c r="I86" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="J86" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="K86" s="1">
-        <v>35971</v>
+        <v>36783</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -6411,18 +6267,27 @@
         <v>104</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P86" t="s">
+        <v>363</v>
       </c>
       <c r="Q86" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>59</v>
+        <v>64</v>
+      </c>
+      <c r="B87" s="1">
+        <v>36567</v>
+      </c>
+      <c r="C87" t="s">
+        <v>511</v>
       </c>
       <c r="D87" t="s">
         <v>21</v>
@@ -6430,8 +6295,8 @@
       <c r="E87" t="s">
         <v>21</v>
       </c>
-      <c r="F87" t="s">
-        <v>21</v>
+      <c r="F87">
+        <v>0</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -6440,36 +6305,33 @@
         <v>72</v>
       </c>
       <c r="I87" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="J87" t="s">
-        <v>51</v>
+        <v>364</v>
       </c>
       <c r="K87" s="1">
-        <v>35940</v>
+        <v>36685</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87">
-        <v>5</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>601</v>
+        <v>0</v>
+      </c>
+      <c r="P87" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>58</v>
-      </c>
-      <c r="C88" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D88" t="s">
         <v>21</v>
@@ -6487,19 +6349,19 @@
         <v>72</v>
       </c>
       <c r="I88" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="J88" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="K88" s="1">
-        <v>35958</v>
+        <v>36552</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -6507,57 +6369,69 @@
       <c r="O88">
         <v>0</v>
       </c>
+      <c r="P88" t="s">
+        <v>369</v>
+      </c>
       <c r="Q88" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
+        <v>62</v>
+      </c>
+      <c r="B89" s="1">
+        <v>35969</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>21</v>
+      </c>
+      <c r="E89" t="s">
+        <v>21</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89" t="s">
+        <v>72</v>
+      </c>
+      <c r="I89" t="s">
+        <v>371</v>
+      </c>
+      <c r="J89" t="s">
+        <v>370</v>
+      </c>
+      <c r="K89" s="1">
+        <v>36482</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
+        <v>74</v>
+      </c>
+      <c r="N89" t="b">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q89">
         <v>57</v>
-      </c>
-      <c r="D89" t="s">
-        <v>21</v>
-      </c>
-      <c r="E89" t="s">
-        <v>21</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-      <c r="H89" t="s">
-        <v>72</v>
-      </c>
-      <c r="I89" t="s">
-        <v>381</v>
-      </c>
-      <c r="J89" t="s">
-        <v>380</v>
-      </c>
-      <c r="K89" s="1">
-        <v>35874</v>
-      </c>
-      <c r="L89" t="b">
-        <v>0</v>
-      </c>
-      <c r="M89" t="s">
-        <v>34</v>
-      </c>
-      <c r="N89" t="b">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>4</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D90" t="s">
         <v>21</v>
@@ -6575,19 +6449,19 @@
         <v>72</v>
       </c>
       <c r="I90" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="J90" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="K90" s="1">
-        <v>35836</v>
+        <v>36322</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
@@ -6598,10 +6472,10 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C91" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
         <v>21</v>
@@ -6619,33 +6493,33 @@
         <v>72</v>
       </c>
       <c r="I91" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J91" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="K91" s="1">
-        <v>35704</v>
+        <v>35971</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
       </c>
       <c r="O91">
         <v>0</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>54</v>
-      </c>
-      <c r="C92" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D92" t="s">
         <v>21</v>
@@ -6653,8 +6527,8 @@
       <c r="E92" t="s">
         <v>21</v>
       </c>
-      <c r="F92">
-        <v>0</v>
+      <c r="F92" t="s">
+        <v>21</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6663,33 +6537,36 @@
         <v>72</v>
       </c>
       <c r="I92" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="J92" t="s">
-        <v>387</v>
+        <v>51</v>
       </c>
       <c r="K92" s="1">
-        <v>35542</v>
+        <v>35940</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
       </c>
       <c r="M92" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q92" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
       </c>
       <c r="D93" t="s">
         <v>21</v>
@@ -6707,13 +6584,13 @@
         <v>72</v>
       </c>
       <c r="I93" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="J93" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="K93" s="1">
-        <v>35500</v>
+        <v>35958</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -6728,12 +6605,12 @@
         <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D94" t="s">
         <v>21</v>
@@ -6751,33 +6628,33 @@
         <v>72</v>
       </c>
       <c r="I94" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="J94" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="K94" s="1">
-        <v>35500</v>
+        <v>35874</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
       </c>
       <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D95" t="s">
         <v>21</v>
@@ -6795,39 +6672,33 @@
         <v>72</v>
       </c>
       <c r="I95" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="J95" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="K95" s="1">
-        <v>35419</v>
+        <v>35836</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
       </c>
       <c r="O95">
         <v>0</v>
-      </c>
-      <c r="P95" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="D96" t="s">
         <v>21</v>
@@ -6845,36 +6716,33 @@
         <v>72</v>
       </c>
       <c r="I96" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="J96" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="K96" s="1">
-        <v>35158</v>
+        <v>35704</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
       </c>
       <c r="O96">
         <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C97" t="s">
-        <v>238</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
         <v>21</v>
@@ -6892,33 +6760,33 @@
         <v>72</v>
       </c>
       <c r="I97" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="J97" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="K97" s="1">
-        <v>35158</v>
+        <v>35542</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
       </c>
       <c r="M97" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
       </c>
       <c r="O97">
         <v>0</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>48</v>
-      </c>
-      <c r="C98" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="D98" t="s">
         <v>21</v>
@@ -6936,19 +6804,19 @@
         <v>72</v>
       </c>
       <c r="I98" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="J98" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="K98" s="1">
-        <v>35131</v>
+        <v>35500</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="N98" t="b">
         <v>0</v>
@@ -6956,19 +6824,13 @@
       <c r="O98">
         <v>0</v>
       </c>
-      <c r="P98" t="s">
-        <v>402</v>
+      <c r="Q98" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>47</v>
-      </c>
-      <c r="B99" s="1">
-        <v>34596</v>
-      </c>
-      <c r="C99" t="s">
-        <v>196</v>
+        <v>52</v>
       </c>
       <c r="D99" t="s">
         <v>21</v>
@@ -6986,19 +6848,19 @@
         <v>72</v>
       </c>
       <c r="I99" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="J99" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="K99" s="1">
-        <v>35074</v>
+        <v>35500</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="N99" t="b">
         <v>0</v>
@@ -7006,13 +6868,13 @@
       <c r="O99">
         <v>0</v>
       </c>
-      <c r="P99" t="s">
-        <v>405</v>
+      <c r="Q99">
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D100" t="s">
         <v>21</v>
@@ -7030,19 +6892,19 @@
         <v>72</v>
       </c>
       <c r="I100" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="J100" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="K100" s="1">
-        <v>35002</v>
+        <v>35419</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -7050,16 +6912,19 @@
       <c r="O100">
         <v>0</v>
       </c>
+      <c r="P100" t="s">
+        <v>395</v>
+      </c>
       <c r="Q100" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>7</v>
+        <v>238</v>
       </c>
       <c r="D101" t="s">
         <v>21</v>
@@ -7077,19 +6942,19 @@
         <v>72</v>
       </c>
       <c r="I101" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="J101" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="K101" s="1">
-        <v>34850</v>
+        <v>35158</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
       </c>
       <c r="M101" t="s">
-        <v>34</v>
+        <v>179</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
@@ -7098,12 +6963,15 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="C102" t="s">
+        <v>238</v>
       </c>
       <c r="D102" t="s">
         <v>21</v>
@@ -7111,8 +6979,8 @@
       <c r="E102" t="s">
         <v>21</v>
       </c>
-      <c r="F102" t="s">
-        <v>21</v>
+      <c r="F102">
+        <v>0</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -7121,13 +6989,13 @@
         <v>72</v>
       </c>
       <c r="I102" t="s">
-        <v>53</v>
+        <v>399</v>
       </c>
       <c r="J102" t="s">
-        <v>54</v>
+        <v>398</v>
       </c>
       <c r="K102" s="1">
-        <v>34669</v>
+        <v>35158</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -7144,13 +7012,10 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>43</v>
-      </c>
-      <c r="B103" s="2">
-        <v>34060</v>
+        <v>48</v>
       </c>
       <c r="C103" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="D103" t="s">
         <v>21</v>
@@ -7168,33 +7033,39 @@
         <v>72</v>
       </c>
       <c r="I103" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="J103" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="K103" s="1">
-        <v>34661</v>
+        <v>35131</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
       </c>
       <c r="O103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P103" t="s">
-        <v>517</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="B104" s="1">
+        <v>34596</v>
+      </c>
+      <c r="C104" t="s">
+        <v>196</v>
       </c>
       <c r="D104" t="s">
         <v>21</v>
@@ -7212,19 +7083,19 @@
         <v>72</v>
       </c>
       <c r="I104" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="J104" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="K104" s="1">
-        <v>34423</v>
+        <v>35074</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
@@ -7232,13 +7103,13 @@
       <c r="O104">
         <v>0</v>
       </c>
-      <c r="Q104" t="s">
-        <v>594</v>
+      <c r="P104" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D105" t="s">
         <v>21</v>
@@ -7256,30 +7127,33 @@
         <v>72</v>
       </c>
       <c r="I105" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="J105" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="K105" s="1">
-        <v>34320</v>
+        <v>35002</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
       </c>
       <c r="O105">
         <v>0</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C106" t="s">
         <v>7</v>
@@ -7300,33 +7174,33 @@
         <v>72</v>
       </c>
       <c r="I106" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="J106" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="K106" s="1">
-        <v>34320</v>
+        <v>34850</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>179</v>
+        <v>34</v>
       </c>
       <c r="N106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106">
         <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>39</v>
-      </c>
-      <c r="C107" t="s">
-        <v>420</v>
+        <v>44</v>
       </c>
       <c r="D107" t="s">
         <v>21</v>
@@ -7334,8 +7208,8 @@
       <c r="E107" t="s">
         <v>21</v>
       </c>
-      <c r="F107">
-        <v>0</v>
+      <c r="F107" t="s">
+        <v>21</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -7344,19 +7218,19 @@
         <v>72</v>
       </c>
       <c r="I107" t="s">
-        <v>419</v>
+        <v>53</v>
       </c>
       <c r="J107" t="s">
-        <v>418</v>
+        <v>54</v>
       </c>
       <c r="K107" s="1">
-        <v>34310</v>
+        <v>34669</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -7367,10 +7241,13 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="B108" s="2">
+        <v>34060</v>
       </c>
       <c r="C108" t="s">
-        <v>423</v>
+        <v>7</v>
       </c>
       <c r="D108" t="s">
         <v>21</v>
@@ -7388,33 +7265,33 @@
         <v>72</v>
       </c>
       <c r="I108" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="J108" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="K108" s="1">
-        <v>34256</v>
+        <v>34661</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P108" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>37</v>
-      </c>
-      <c r="C109" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="D109" t="s">
         <v>21</v>
@@ -7432,19 +7309,19 @@
         <v>72</v>
       </c>
       <c r="I109" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="J109" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="K109" s="1">
-        <v>34142</v>
+        <v>34423</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
       </c>
       <c r="M109" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
@@ -7452,13 +7329,13 @@
       <c r="O109">
         <v>0</v>
       </c>
-      <c r="Q109">
-        <v>5</v>
+      <c r="Q109" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D110" t="s">
         <v>21</v>
@@ -7476,36 +7353,33 @@
         <v>72</v>
       </c>
       <c r="I110" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="J110" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="K110" s="1">
-        <v>34142</v>
+        <v>34320</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="N110" t="b">
         <v>0</v>
       </c>
       <c r="O110">
         <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C111" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="D111" t="s">
         <v>21</v>
@@ -7523,22 +7397,22 @@
         <v>72</v>
       </c>
       <c r="I111" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="J111" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="K111" s="1">
-        <v>34107</v>
+        <v>34320</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="N111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -7546,7 +7420,10 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="C112" t="s">
+        <v>420</v>
       </c>
       <c r="D112" t="s">
         <v>21</v>
@@ -7564,19 +7441,19 @@
         <v>72</v>
       </c>
       <c r="I112" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="J112" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="K112" s="1">
-        <v>34009</v>
+        <v>34310</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -7587,7 +7464,10 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="C113" t="s">
+        <v>423</v>
       </c>
       <c r="D113" t="s">
         <v>21</v>
@@ -7605,36 +7485,33 @@
         <v>72</v>
       </c>
       <c r="I113" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="J113" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="K113" s="1">
-        <v>33988</v>
+        <v>34256</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
       </c>
       <c r="O113">
         <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="D114" t="s">
         <v>21</v>
@@ -7652,19 +7529,19 @@
         <v>72</v>
       </c>
       <c r="I114" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="J114" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="K114" s="1">
-        <v>33795</v>
+        <v>34142</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>158</v>
+        <v>52</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -7672,13 +7549,13 @@
       <c r="O114">
         <v>0</v>
       </c>
-      <c r="P114" t="s">
-        <v>436</v>
+      <c r="Q114">
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s">
         <v>21</v>
@@ -7696,19 +7573,19 @@
         <v>72</v>
       </c>
       <c r="I115" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="J115" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="K115" s="1">
-        <v>33691</v>
+        <v>34142</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -7717,12 +7594,15 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="C116" t="s">
+        <v>238</v>
       </c>
       <c r="D116" t="s">
         <v>21</v>
@@ -7740,33 +7620,30 @@
         <v>72</v>
       </c>
       <c r="I116" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="J116" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="K116" s="1">
-        <v>33630</v>
+        <v>34107</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
       </c>
       <c r="O116">
         <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D117" t="s">
         <v>21</v>
@@ -7784,33 +7661,30 @@
         <v>72</v>
       </c>
       <c r="I117" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="J117" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="K117" s="1">
-        <v>33630</v>
+        <v>34009</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
       </c>
       <c r="M117" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
       </c>
       <c r="O117">
         <v>0</v>
-      </c>
-      <c r="P117" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D118" t="s">
         <v>21</v>
@@ -7828,19 +7702,19 @@
         <v>72</v>
       </c>
       <c r="I118" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="J118" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="K118" s="1">
-        <v>33574</v>
+        <v>33988</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="N118" t="b">
         <v>0</v>
@@ -7848,16 +7722,16 @@
       <c r="O118">
         <v>0</v>
       </c>
-      <c r="P118" t="s">
-        <v>446</v>
+      <c r="Q118">
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C119" t="s">
-        <v>449</v>
+        <v>14</v>
       </c>
       <c r="D119" t="s">
         <v>21</v>
@@ -7875,19 +7749,19 @@
         <v>72</v>
       </c>
       <c r="I119" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="J119" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="K119" s="1">
-        <v>33574</v>
+        <v>33795</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
       </c>
       <c r="M119" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -7896,15 +7770,12 @@
         <v>0</v>
       </c>
       <c r="P119" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>593</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D120" t="s">
         <v>21</v>
@@ -7922,30 +7793,33 @@
         <v>72</v>
       </c>
       <c r="I120" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="J120" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="K120" s="1">
-        <v>33413</v>
+        <v>33691</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
       </c>
       <c r="O120">
         <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D121" t="s">
         <v>21</v>
@@ -7963,13 +7837,13 @@
         <v>72</v>
       </c>
       <c r="I121" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="J121" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="K121" s="1">
-        <v>33413</v>
+        <v>33630</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -7984,12 +7858,12 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D122" t="s">
         <v>21</v>
@@ -8007,30 +7881,33 @@
         <v>72</v>
       </c>
       <c r="I122" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="J122" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="K122" s="1">
-        <v>33413</v>
+        <v>33630</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>179</v>
+        <v>34</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
+      </c>
+      <c r="P122" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D123" t="s">
         <v>21</v>
@@ -8048,19 +7925,19 @@
         <v>72</v>
       </c>
       <c r="I123" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="J123" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="K123" s="1">
-        <v>33220</v>
+        <v>33574</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="N123" t="b">
         <v>0</v>
@@ -8068,13 +7945,16 @@
       <c r="O123">
         <v>0</v>
       </c>
-      <c r="Q123">
-        <v>1</v>
+      <c r="P123" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="C124" t="s">
+        <v>449</v>
       </c>
       <c r="D124" t="s">
         <v>21</v>
@@ -8092,13 +7972,13 @@
         <v>72</v>
       </c>
       <c r="I124" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="J124" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="K124" s="1">
-        <v>33220</v>
+        <v>33574</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -8112,13 +7992,16 @@
       <c r="O124">
         <v>0</v>
       </c>
-      <c r="Q124">
-        <v>20</v>
+      <c r="P124" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D125" t="s">
         <v>21</v>
@@ -8136,33 +8019,30 @@
         <v>72</v>
       </c>
       <c r="I125" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="J125" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="K125" s="1">
-        <v>33220</v>
+        <v>33413</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
       </c>
       <c r="O125">
         <v>0</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D126" t="s">
         <v>21</v>
@@ -8180,19 +8060,19 @@
         <v>72</v>
       </c>
       <c r="I126" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="J126" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="K126" s="1">
-        <v>33072</v>
+        <v>33413</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -8200,13 +8080,13 @@
       <c r="O126">
         <v>0</v>
       </c>
-      <c r="Q126" t="s">
-        <v>591</v>
+      <c r="Q126">
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D127" t="s">
         <v>21</v>
@@ -8224,33 +8104,30 @@
         <v>72</v>
       </c>
       <c r="I127" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="J127" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="K127" s="1">
-        <v>33072</v>
+        <v>33413</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
       </c>
       <c r="O127">
         <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D128" t="s">
         <v>21</v>
@@ -8268,19 +8145,19 @@
         <v>72</v>
       </c>
       <c r="I128" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="J128" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="K128" s="1">
-        <v>32857</v>
+        <v>33220</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
@@ -8294,7 +8171,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D129" t="s">
         <v>21</v>
@@ -8312,13 +8189,13 @@
         <v>72</v>
       </c>
       <c r="I129" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="J129" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="K129" s="1">
-        <v>32857</v>
+        <v>33220</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -8332,10 +8209,13 @@
       <c r="O129">
         <v>0</v>
       </c>
+      <c r="Q129">
+        <v>20</v>
+      </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D130" t="s">
         <v>21</v>
@@ -8353,33 +8233,33 @@
         <v>72</v>
       </c>
       <c r="I130" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="J130" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="K130" s="1">
-        <v>32797</v>
+        <v>33220</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="N130" t="b">
         <v>0</v>
       </c>
       <c r="O130">
         <v>0</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>15</v>
-      </c>
-      <c r="C131" t="s">
-        <v>473</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
         <v>21</v>
@@ -8397,33 +8277,33 @@
         <v>72</v>
       </c>
       <c r="I131" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="J131" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="K131" s="1">
-        <v>32797</v>
+        <v>33072</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
       </c>
       <c r="O131">
         <v>0</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>14</v>
-      </c>
-      <c r="C132" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D132" t="s">
         <v>21</v>
@@ -8441,30 +8321,33 @@
         <v>72</v>
       </c>
       <c r="I132" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J132" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="K132" s="1">
-        <v>32493</v>
+        <v>33072</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
       </c>
       <c r="M132" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
       </c>
       <c r="O132">
         <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D133" t="s">
         <v>21</v>
@@ -8482,19 +8365,19 @@
         <v>72</v>
       </c>
       <c r="I133" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="J133" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="K133" s="1">
-        <v>32454</v>
+        <v>32857</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
       </c>
       <c r="M133" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
@@ -8503,12 +8386,12 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
         <v>21</v>
@@ -8526,33 +8409,30 @@
         <v>72</v>
       </c>
       <c r="I134" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="J134" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="K134" s="1">
-        <v>32454</v>
+        <v>32857</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
       </c>
       <c r="O134">
         <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D135" t="s">
         <v>21</v>
@@ -8570,13 +8450,13 @@
         <v>72</v>
       </c>
       <c r="I135" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="J135" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="K135" s="1">
-        <v>32117</v>
+        <v>32797</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -8593,10 +8473,10 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>238</v>
+        <v>473</v>
       </c>
       <c r="D136" t="s">
         <v>21</v>
@@ -8614,22 +8494,22 @@
         <v>72</v>
       </c>
       <c r="I136" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="J136" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="K136" s="1">
-        <v>32127</v>
+        <v>32797</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
       </c>
       <c r="M136" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="N136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -8637,7 +8517,10 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="C137" t="s">
+        <v>14</v>
       </c>
       <c r="D137" t="s">
         <v>21</v>
@@ -8655,19 +8538,19 @@
         <v>72</v>
       </c>
       <c r="I137" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="J137" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="K137" s="1">
-        <v>31831</v>
+        <v>32493</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -8678,7 +8561,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D138" t="s">
         <v>21</v>
@@ -8696,80 +8579,77 @@
         <v>72</v>
       </c>
       <c r="I138" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="J138" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="K138" s="1">
-        <v>31761</v>
+        <v>32454</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="N138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138">
         <v>0</v>
       </c>
-      <c r="Q138" t="s">
-        <v>590</v>
+      <c r="Q138">
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
+        <v>12</v>
+      </c>
+      <c r="D139" t="s">
+        <v>21</v>
+      </c>
+      <c r="E139" t="s">
+        <v>21</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139" t="s">
+        <v>72</v>
+      </c>
+      <c r="I139" t="s">
+        <v>479</v>
+      </c>
+      <c r="J139" t="s">
+        <v>478</v>
+      </c>
+      <c r="K139" s="1">
+        <v>32454</v>
+      </c>
+      <c r="L139" t="b">
+        <v>0</v>
+      </c>
+      <c r="M139" t="s">
+        <v>22</v>
+      </c>
+      <c r="N139" t="b">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
         <v>7</v>
-      </c>
-      <c r="C139" t="s">
-        <v>238</v>
-      </c>
-      <c r="D139" t="s">
-        <v>21</v>
-      </c>
-      <c r="E139" t="s">
-        <v>21</v>
-      </c>
-      <c r="F139">
-        <v>0</v>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139" t="s">
-        <v>72</v>
-      </c>
-      <c r="I139" t="s">
-        <v>489</v>
-      </c>
-      <c r="J139" t="s">
-        <v>488</v>
-      </c>
-      <c r="K139" s="1">
-        <v>31467</v>
-      </c>
-      <c r="L139" t="b">
-        <v>0</v>
-      </c>
-      <c r="M139" t="s">
-        <v>158</v>
-      </c>
-      <c r="N139" t="b">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>6</v>
-      </c>
-      <c r="C140" t="s">
-        <v>492</v>
+        <v>11</v>
       </c>
       <c r="D140" t="s">
         <v>21</v>
@@ -8787,13 +8667,13 @@
         <v>72</v>
       </c>
       <c r="I140" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J140" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="K140" s="1">
-        <v>31180</v>
+        <v>32117</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -8810,7 +8690,10 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="C141" t="s">
+        <v>238</v>
       </c>
       <c r="D141" t="s">
         <v>21</v>
@@ -8828,33 +8711,30 @@
         <v>72</v>
       </c>
       <c r="I141" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="J141" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="K141" s="1">
-        <v>31180</v>
+        <v>32127</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="N141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>4</v>
-      </c>
-      <c r="C142" t="s">
-        <v>220</v>
+        <v>9</v>
       </c>
       <c r="D142" t="s">
         <v>21</v>
@@ -8872,33 +8752,30 @@
         <v>72</v>
       </c>
       <c r="I142" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="J142" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="K142" s="1">
-        <v>31173</v>
+        <v>31831</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="N142" t="b">
         <v>0</v>
       </c>
       <c r="O142">
         <v>0</v>
-      </c>
-      <c r="P142" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D143" t="s">
         <v>21</v>
@@ -8916,33 +8793,36 @@
         <v>72</v>
       </c>
       <c r="I143" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="J143" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="K143" s="1">
-        <v>30978</v>
+        <v>31761</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="N143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143">
         <v>0</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C144" t="s">
-        <v>14</v>
+        <v>238</v>
       </c>
       <c r="D144" t="s">
         <v>21</v>
@@ -8960,13 +8840,13 @@
         <v>72</v>
       </c>
       <c r="I144" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="J144" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="K144" s="1">
-        <v>30964</v>
+        <v>31467</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -8981,47 +8861,264 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145">
+        <v>6</v>
+      </c>
+      <c r="C145" t="s">
+        <v>492</v>
+      </c>
+      <c r="D145" t="s">
+        <v>21</v>
+      </c>
+      <c r="E145" t="s">
+        <v>21</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145" t="s">
+        <v>72</v>
+      </c>
+      <c r="I145" t="s">
+        <v>491</v>
+      </c>
+      <c r="J145" t="s">
+        <v>490</v>
+      </c>
+      <c r="K145" s="1">
+        <v>31180</v>
+      </c>
+      <c r="L145" t="b">
+        <v>0</v>
+      </c>
+      <c r="M145" t="s">
+        <v>132</v>
+      </c>
+      <c r="N145" t="b">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>5</v>
+      </c>
+      <c r="D146" t="s">
+        <v>21</v>
+      </c>
+      <c r="E146" t="s">
+        <v>21</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146" t="s">
+        <v>72</v>
+      </c>
+      <c r="I146" t="s">
+        <v>494</v>
+      </c>
+      <c r="J146" t="s">
+        <v>493</v>
+      </c>
+      <c r="K146" s="1">
+        <v>31180</v>
+      </c>
+      <c r="L146" t="b">
+        <v>0</v>
+      </c>
+      <c r="M146" t="s">
+        <v>69</v>
+      </c>
+      <c r="N146" t="b">
+        <v>0</v>
+      </c>
+      <c r="O146">
         <v>1</v>
       </c>
-      <c r="C145" t="s">
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>220</v>
+      </c>
+      <c r="D147" t="s">
+        <v>21</v>
+      </c>
+      <c r="E147" t="s">
+        <v>21</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147" t="s">
+        <v>72</v>
+      </c>
+      <c r="I147" t="s">
+        <v>496</v>
+      </c>
+      <c r="J147" t="s">
+        <v>495</v>
+      </c>
+      <c r="K147" s="1">
+        <v>31173</v>
+      </c>
+      <c r="L147" t="b">
+        <v>0</v>
+      </c>
+      <c r="M147" t="s">
+        <v>132</v>
+      </c>
+      <c r="N147" t="b">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>3</v>
+      </c>
+      <c r="D148" t="s">
+        <v>21</v>
+      </c>
+      <c r="E148" t="s">
+        <v>21</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148" t="s">
+        <v>72</v>
+      </c>
+      <c r="I148" t="s">
+        <v>499</v>
+      </c>
+      <c r="J148" t="s">
+        <v>498</v>
+      </c>
+      <c r="K148" s="1">
+        <v>30978</v>
+      </c>
+      <c r="L148" t="b">
+        <v>0</v>
+      </c>
+      <c r="M148" t="s">
+        <v>104</v>
+      </c>
+      <c r="N148" t="b">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" t="s">
+        <v>21</v>
+      </c>
+      <c r="E149" t="s">
+        <v>21</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149" t="s">
+        <v>72</v>
+      </c>
+      <c r="I149" t="s">
+        <v>501</v>
+      </c>
+      <c r="J149" t="s">
+        <v>500</v>
+      </c>
+      <c r="K149" s="1">
+        <v>30964</v>
+      </c>
+      <c r="L149" t="b">
+        <v>0</v>
+      </c>
+      <c r="M149" t="s">
+        <v>158</v>
+      </c>
+      <c r="N149" t="b">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
         <v>90</v>
       </c>
-      <c r="D145" t="s">
-        <v>21</v>
-      </c>
-      <c r="E145" t="s">
-        <v>21</v>
-      </c>
-      <c r="F145">
-        <v>0</v>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145" t="s">
-        <v>72</v>
-      </c>
-      <c r="I145" t="s">
+      <c r="D150" t="s">
+        <v>21</v>
+      </c>
+      <c r="E150" t="s">
+        <v>21</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150" t="s">
+        <v>72</v>
+      </c>
+      <c r="I150" t="s">
         <v>503</v>
       </c>
-      <c r="J145" t="s">
+      <c r="J150" t="s">
         <v>502</v>
       </c>
-      <c r="K145" s="1">
+      <c r="K150" s="1">
         <v>30824</v>
       </c>
-      <c r="L145" t="b">
-        <v>0</v>
-      </c>
-      <c r="M145" t="s">
+      <c r="L150" t="b">
+        <v>0</v>
+      </c>
+      <c r="M150" t="s">
         <v>22</v>
       </c>
-      <c r="N145" t="b">
-        <v>0</v>
-      </c>
-      <c r="O145">
+      <c r="N150" t="b">
+        <v>0</v>
+      </c>
+      <c r="O150">
         <v>0</v>
       </c>
     </row>
